--- a/artfynd/A 59038-2024 artfynd.xlsx
+++ b/artfynd/A 59038-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115944345</v>
+        <v>115944340</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530896</v>
+        <v>530947</v>
       </c>
       <c r="R2" t="n">
-        <v>7237086</v>
+        <v>7237089</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115944403</v>
+        <v>115944339</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530863</v>
+        <v>530885</v>
       </c>
       <c r="R3" t="n">
-        <v>7236950</v>
+        <v>7237090</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,16 +890,11 @@
         <v>115944365</v>
       </c>
       <c r="B4" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1012,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115944392</v>
+        <v>115944342</v>
       </c>
       <c r="B5" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530906</v>
+        <v>530915</v>
       </c>
       <c r="R5" t="n">
-        <v>7236977</v>
+        <v>7237089</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115944394</v>
+        <v>115944369</v>
       </c>
       <c r="B6" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530893</v>
+        <v>530959</v>
       </c>
       <c r="R6" t="n">
-        <v>7236975</v>
+        <v>7237007</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115944370</v>
+        <v>115944410</v>
       </c>
       <c r="B7" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530984</v>
+        <v>530909</v>
       </c>
       <c r="R7" t="n">
-        <v>7237006</v>
+        <v>7236925</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1334,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Julia Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1345,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115944342</v>
+        <v>115944370</v>
       </c>
       <c r="B8" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530915</v>
+        <v>530984</v>
       </c>
       <c r="R8" t="n">
-        <v>7237089</v>
+        <v>7237006</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115944410</v>
+        <v>115944344</v>
       </c>
       <c r="B9" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530909</v>
+        <v>530900</v>
       </c>
       <c r="R9" t="n">
-        <v>7236925</v>
+        <v>7237087</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1556,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1567,55 +1523,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115944389</v>
+        <v>115944394</v>
       </c>
       <c r="B10" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530916</v>
+        <v>530893</v>
       </c>
       <c r="R10" t="n">
-        <v>7236980</v>
+        <v>7236975</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1661,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1672,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1683,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115944344</v>
+        <v>115944345</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530900</v>
+        <v>530896</v>
       </c>
       <c r="R11" t="n">
-        <v>7237087</v>
+        <v>7237086</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1797,12 +1738,7 @@
         <v>115944347</v>
       </c>
       <c r="B12" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115944369</v>
+        <v>115944389</v>
       </c>
       <c r="B13" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,34 +1852,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530959</v>
+        <v>530916</v>
       </c>
       <c r="R13" t="n">
-        <v>7237007</v>
+        <v>7236980</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,7 +1930,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2005,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Julia Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2016,15 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115944339</v>
+        <v>115944403</v>
       </c>
       <c r="B14" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2032,34 +1963,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>314</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530885</v>
+        <v>530863</v>
       </c>
       <c r="R14" t="n">
-        <v>7237090</v>
+        <v>7236950</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,7 +2040,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
